--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>103 filas de datos</t>
+          <t>102 filas de datos</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-064</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5071,19 +5071,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«10»</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-065</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5170,37 +5170,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5225,19 +5225,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>definicion_operativa</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>el artículo no define qué contaba como éxito</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-073</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5247,27 +5247,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5302,19 +5302,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5324,22 +5324,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5384,14 +5384,14 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-078</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5555,37 +5555,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5632,37 +5632,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-081</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5709,37 +5709,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5769,14 +5769,14 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5786,37 +5786,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5846,14 +5846,14 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5930,7 +5930,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6000,14 +6000,14 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6077,14 +6077,14 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo no aleatorizado</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6191,22 +6191,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6226,19 +6226,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«NA»</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-098</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6303,19 +6303,19 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«NA»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6325,22 +6325,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6469,7 +6469,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«20»</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«20»</t>
+          <t>éxito clínico n=«NA» sobre N=«17»</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«17»</t>
+          <t>éxito clínico n=«NA» sobre N=«11»</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6770,24 +6770,24 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«11»</t>
+          <t>éxito clínico n=«NA» sobre N=«2»</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-110</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6797,22 +6797,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6842,19 +6842,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«2»</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-110</t>
+          <t>EST-115</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>otra</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-115</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>ensayo no aleatorizado</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6951,17 +6951,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6996,19 +6996,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«260»</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7018,17 +7018,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7073,19 +7073,19 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«260»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-117</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>sí</t>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7162,7 +7162,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-121</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7232,14 +7232,14 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7309,14 +7309,14 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7381,19 +7381,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>definicion_operativa</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>el artículo no define qué contaba como éxito</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-133</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7403,27 +7403,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7458,19 +7458,19 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-133</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7510,17 +7510,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7540,14 +7540,14 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7557,17 +7557,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7617,14 +7617,14 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-140</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7634,37 +7634,37 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7694,14 +7694,14 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-140</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7711,47 +7711,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7766,19 +7766,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>atribuible_a_P_aeruginosa</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>el numerador no es una proporción de P. aeruginosa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7843,19 +7843,19 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>atribuible_a_P_aeruginosa</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>el numerador no es una proporción de P. aeruginosa</t>
+          <t>éxito clínico n=«NA» sobre N=«27»</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-152</t>
+          <t>EST-157</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7925,14 +7925,14 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«27»</t>
+          <t>éxito clínico n=«NA» sobre N=«30»</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-157</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7942,27 +7942,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7997,19 +7997,19 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«30»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-165</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8019,27 +8019,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>cohorte prospectiva</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«48»</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EST-165</t>
+          <t>EST-167</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>cohorte prospectiva</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8151,19 +8151,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«48»</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EST-167</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8233,14 +8233,14 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8250,17 +8250,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8310,14 +8310,14 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EST-170</t>
+          <t>EST-173</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8327,37 +8327,37 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8387,14 +8387,14 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EST-173</t>
+          <t>EST-181</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8404,47 +8404,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8464,14 +8464,14 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EST-181</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8548,7 +8548,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EST-184</t>
+          <t>EST-188</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8558,47 +8558,47 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8618,14 +8618,14 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EST-188</t>
+          <t>EST-208</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8635,42 +8635,42 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8695,89 +8695,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>EST-208</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
           <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O104"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>102 filas de datos</t>
+          <t>98 filas de datos</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1849,7 +1849,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-010</t>
+          <t>EST-011</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-011</t>
+          <t>EST-012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-013</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2157,7 +2157,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-013</t>
+          <t>EST-014</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-014</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2388,7 +2388,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-018</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-018</t>
+          <t>EST-019</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2535,14 +2535,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EST-019</t>
+          <t>EST-021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2602,24 +2602,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>proporcion_no_tiempo</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>el desenlace principal es un tiempo, no una proporción</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EST-021</t>
+          <t>EST-024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2679,24 +2679,24 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>proporcion_no_tiempo</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>el desenlace principal es un tiempo, no una proporción</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-024</t>
+          <t>EST-027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2766,14 +2766,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EST-027</t>
+          <t>EST-028</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2783,22 +2783,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EST-028</t>
+          <t>EST-029</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2915,19 +2915,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«19»</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EST-029</t>
+          <t>EST-030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,27 +2937,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2992,19 +2992,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«19»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EST-030</t>
+          <t>EST-031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3014,17 +3014,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EST-031</t>
+          <t>EST-032</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3091,42 +3091,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EST-032</t>
+          <t>EST-033</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EST-033</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3245,37 +3245,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3305,14 +3305,14 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EST-034</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-039</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EST-039</t>
+          <t>EST-040</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3536,14 +3536,14 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EST-040</t>
+          <t>EST-042</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EST-042</t>
+          <t>EST-043</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EST-043</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-045</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3784,37 +3784,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EST-045</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3861,37 +3861,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EST-046</t>
+          <t>EST-047</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST-047</t>
+          <t>EST-048</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EST-048</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-050</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4236,7 +4236,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EST-050</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-054</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4400,37 +4400,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4460,14 +4460,14 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EST-054</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4477,37 +4477,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4554,17 +4554,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4609,19 +4609,19 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«178»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-059</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4691,14 +4691,14 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4708,17 +4708,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4768,14 +4768,14 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EST-059</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,22 +4785,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-064</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4862,37 +4862,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4922,14 +4922,14 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-065</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4939,37 +4939,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5016,37 +5016,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5071,19 +5071,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>definicion_operativa</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>el artículo no define qué contaba como éxito</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-073</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,17 +5093,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>otra</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5225,19 +5225,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5247,22 +5247,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5391,7 +5391,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-078</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5401,37 +5401,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-081</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5622,7 +5622,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5632,19 +5632,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>sí</t>
@@ -5692,14 +5692,14 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5709,37 +5709,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5769,14 +5769,14 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5846,14 +5846,14 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5930,7 +5930,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6000,14 +6000,14 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo no aleatorizado</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6037,22 +6037,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6072,19 +6072,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«NA»</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-098</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6094,22 +6094,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6154,14 +6154,14 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6191,22 +6191,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6226,19 +6226,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«NA»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6308,14 +6308,14 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6380,39 +6380,39 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«20»</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«17»</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«20»</t>
+          <t>éxito clínico n=«NA» sobre N=«11»</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«17»</t>
+          <t>éxito clínico n=«NA» sobre N=«2»</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-110</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6643,22 +6643,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6688,29 +6688,29 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«11»</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-115</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6720,17 +6720,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6765,19 +6765,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«2»</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-110</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6787,32 +6787,32 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>ensayo no aleatorizado</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6842,19 +6842,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«260»</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-115</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6864,22 +6864,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6941,17 +6941,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6971,17 +6971,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6996,19 +6996,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«260»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-117</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7078,14 +7078,14 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-121</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7162,7 +7162,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7227,19 +7227,19 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>definicion_operativa</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>el artículo no define qué contaba como éxito</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-133</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7249,22 +7249,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7309,14 +7309,14 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7381,19 +7381,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-133</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7403,22 +7403,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7463,14 +7463,14 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-140</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7480,47 +7480,47 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7540,14 +7540,14 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7557,17 +7557,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7612,19 +7612,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>atribuible_a_P_aeruginosa</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>el numerador no es una proporción de P. aeruginosa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-140</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7634,32 +7634,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>cohorte retrospectiva</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7689,19 +7689,19 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«27»</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-157</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7711,22 +7711,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7741,17 +7741,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7766,19 +7766,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>atribuible_a_P_aeruginosa</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>el numerador no es una proporción de P. aeruginosa</t>
+          <t>éxito clínico n=«NA» sobre N=«30»</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-152</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7818,17 +7818,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7843,19 +7843,19 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«27»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-157</t>
+          <t>EST-165</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>cohorte prospectiva</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7925,14 +7925,14 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«30»</t>
+          <t>éxito clínico n=«NA» sobre N=«48»</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-167</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7942,22 +7942,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8002,14 +8002,14 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-165</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8019,27 +8019,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>cohorte prospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«48»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EST-167</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8096,22 +8096,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8156,14 +8156,14 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-173</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8173,37 +8173,37 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -8233,14 +8233,14 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EST-170</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8317,7 +8317,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EST-173</t>
+          <t>EST-188</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8391,316 +8391,8 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>EST-181</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>EST-184</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>EST-188</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>no evaluable</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>EST-208</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>98 filas de datos</t>
+          <t>94 filas de datos</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3774,7 +3774,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EST-045</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3784,37 +3784,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EST-046</t>
+          <t>EST-047</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3928,7 +3928,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EST-047</t>
+          <t>EST-048</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST-048</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-050</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EST-050</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4236,7 +4236,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-054</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4323,37 +4323,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4383,14 +4383,14 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EST-054</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4400,37 +4400,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4460,14 +4460,14 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4544,7 +4544,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4554,17 +4554,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4614,14 +4614,14 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EST-059</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4691,14 +4691,14 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-064</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4708,37 +4708,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4768,14 +4768,14 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-065</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,37 +4785,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4862,37 +4862,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4917,19 +4917,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>definicion_operativa</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>el artículo no define qué contaba como éxito</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-073</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>otra</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5071,19 +5071,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,22 +5093,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-078</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5247,37 +5247,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5391,7 +5391,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-081</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5478,19 +5478,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>sí</t>
@@ -5538,14 +5538,14 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5555,37 +5555,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5776,7 +5776,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5846,14 +5846,14 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5863,17 +5863,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo no aleatorizado</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5883,22 +5883,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5918,19 +5918,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«NA»</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-098</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6000,14 +6000,14 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6037,22 +6037,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6072,19 +6072,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«NA»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6094,22 +6094,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6154,14 +6154,14 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6226,39 +6226,39 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«20»</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«17»</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«20»</t>
+          <t>éxito clínico n=«NA» sobre N=«11»</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6462,24 +6462,24 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«17»</t>
+          <t>éxito clínico n=«NA» sobre N=«2»</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-110</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6489,22 +6489,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6534,29 +6534,29 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«11»</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-115</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6611,19 +6611,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«2»</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EST-110</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>ensayo no aleatorizado</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6688,19 +6688,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«260»</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EST-115</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6770,14 +6770,14 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6787,17 +6787,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6842,19 +6842,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«260»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-117</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-121</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7008,7 +7008,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-133</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7018,22 +7018,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7078,14 +7078,14 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7162,7 +7162,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7227,19 +7227,19 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-133</t>
+          <t>EST-140</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7309,14 +7309,14 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7381,19 +7381,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>atribuible_a_P_aeruginosa</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>el numerador no es una proporción de P. aeruginosa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7403,17 +7403,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7458,19 +7458,19 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«27»</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-140</t>
+          <t>EST-157</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7480,17 +7480,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>ensayo aleatorizado</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7535,19 +7535,19 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«30»</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7557,17 +7557,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7612,19 +7612,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>atribuible_a_P_aeruginosa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>el numerador no es una proporción de P. aeruginosa</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-152</t>
+          <t>EST-165</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>cohorte prospectiva</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7694,14 +7694,14 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«27»</t>
+          <t>éxito clínico n=«NA» sobre N=«48»</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-157</t>
+          <t>EST-167</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7766,19 +7766,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«30»</t>
+          <t>diseño «other»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7855,7 +7855,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-165</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7865,27 +7865,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>cohorte prospectiva</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7920,19 +7920,19 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«48»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-167</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7942,22 +7942,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8002,14 +8002,14 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-188</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8019,37 +8019,37 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>no evaluable</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8079,320 +8079,12 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>EST-170</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>EST-173</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>no evaluable</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
           <t>diseño «NA»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>EST-184</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>EST-188</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>no evaluable</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$O$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>94 filas de datos</t>
+          <t>73 filas de datos</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1541,7 +1541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EST-005</t>
+          <t>EST-006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1618,7 +1618,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EST-006</t>
+          <t>EST-007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EST-007</t>
+          <t>EST-008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1760,19 +1760,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«9»</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EST-008</t>
+          <t>EST-010</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«9»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-010</t>
+          <t>EST-011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-011</t>
+          <t>EST-012</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-013</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-013</t>
+          <t>EST-014</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2157,7 +2157,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-014</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2381,14 +2381,14 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-018</t>
+          <t>EST-021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo aleatorizado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>proporcion_no_tiempo</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>el desenlace principal es un tiempo, no una proporción</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-019</t>
+          <t>EST-024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2542,7 +2542,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EST-021</t>
+          <t>EST-027</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2602,24 +2602,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>proporcion_no_tiempo</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>el desenlace principal es un tiempo, no una proporción</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EST-024</t>
+          <t>EST-030</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-027</t>
+          <t>EST-031</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2766,14 +2766,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EST-028</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2783,22 +2783,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EST-029</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2860,27 +2860,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ensayo aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2915,19 +2915,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«19»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EST-030</t>
+          <t>EST-039</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2997,14 +2997,14 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EST-031</t>
+          <t>EST-040</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3014,17 +3014,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EST-032</t>
+          <t>EST-042</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3091,37 +3091,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EST-033</t>
+          <t>EST-043</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3168,37 +3168,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EST-034</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3305,14 +3305,14 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3382,14 +3382,14 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EST-039</t>
+          <t>EST-047</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3399,17 +3399,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3459,14 +3459,14 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EST-040</t>
+          <t>EST-048</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3543,7 +3543,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EST-042</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EST-043</t>
+          <t>EST-050</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EST-046</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3851,7 +3851,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EST-047</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3928,7 +3928,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EST-048</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4075,14 +4075,14 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EST-050</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4169,17 +4169,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4224,19 +4224,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>definicion_operativa</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>el artículo no define qué contaba como éxito</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4246,17 +4246,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4306,14 +4306,14 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EST-054</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4323,37 +4323,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4383,14 +4383,14 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4400,17 +4400,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4460,14 +4460,14 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4554,17 +4554,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4614,14 +4614,14 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4698,7 +4698,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4708,37 +4708,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4768,14 +4768,14 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4785,37 +4785,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4917,19 +4917,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>el artículo no define qué contaba como éxito</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>ensayo no aleatorizado</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4949,22 +4949,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4994,19 +4994,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>diseño «other»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«NA»</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,17 +5093,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5225,54 +5225,54 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«20»</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>cohorte retrospectiva</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5302,39 +5302,39 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«17»</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5379,54 +5379,54 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«11»</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>cohorte retrospectiva</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>no evaluable</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5456,19 +5456,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«2»</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>ensayo no aleatorizado</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5533,19 +5533,19 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«260»</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5637,12 +5637,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5776,7 +5776,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5846,14 +5846,14 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5863,17 +5863,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ensayo no aleatorizado</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5883,17 +5883,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5918,19 +5918,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«NA»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>serie de casos</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6000,14 +6000,14 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6072,19 +6072,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>atribuible_a_P_aeruginosa</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>el numerador no es una proporción de P. aeruginosa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6094,17 +6094,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>reporte de caso único</t>
+          <t>cohorte retrospectiva</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6149,19 +6149,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>numerador_valido</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
+          <t>éxito clínico n=«NA» sobre N=«27»</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6226,39 +6226,39 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«20»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>serie de casos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6303,39 +6303,39 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«17»</t>
+          <t>diseño «case series»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6355,17 +6355,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6380,39 +6380,39 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«11»</t>
+          <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>cohorte retrospectiva</t>
+          <t>reporte de caso único</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>no cumple</t>
+          <t>cumple</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>no cumple</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6457,1634 +6457,17 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>diseno_comparativo</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>éxito clínico n=«NA» sobre N=«2»</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>EST-110</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>no evaluable</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>EST-115</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>otra</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>diseño «other»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>EST-116</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ensayo no aleatorizado</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>numerador_valido</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>éxito clínico n=«NA» sobre N=«260»</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>EST-117</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>serie de casos</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>EST-121</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>serie de casos</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>EST-124</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
           <t>diseño «case report»: sin grupo de comparación</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>EST-129</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>serie de casos</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>EST-133</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>otra</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>diseño «other»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>EST-134</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>serie de casos</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>EST-135</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>EST-140</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>no evaluable</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>cohorte retrospectiva</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>atribuible_a_P_aeruginosa</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>el numerador no es una proporción de P. aeruginosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>cohorte retrospectiva</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>numerador_valido</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>éxito clínico n=«NA» sobre N=«27»</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>EST-157</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>ensayo aleatorizado</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>numerador_valido</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>éxito clínico n=«NA» sobre N=«30»</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>EST-164</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>serie de casos</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>EST-165</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>cohorte prospectiva</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>numerador_valido</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>éxito clínico n=«NA» sobre N=«48»</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>EST-167</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>otra</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>diseño «other»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>EST-169</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>serie de casos</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>diseño «case series»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>EST-170</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>EST-184</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>reporte de caso único</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>diseño «case report»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>EST-188</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>no evaluable</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>no cumple</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>cumple</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>diseño «NA»: sin grupo de comparación</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O95"/>
+  <autoFilter ref="A1:O74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-12</t>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -733,7 +733,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>La tabla del embudo de agregabilidad desglosada brazo a brazo: si cada brazo cumple cada requisito de una proporción agrupada de éxito clínico («cumple», «no cumple» o «no evaluable»), el primero que falla y por qué. La calcula el canal (build_tabla6_brazos.py) sobre la extracción adjudicada (S14), con las reglas del embudo, y se detiene si sus recuentos no coinciden con los publicados. «¿Texto completo obtenido?» no es uno de los requisitos.</t>
         </is>
       </c>
     </row>
@@ -514,224 +521,235 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 3.6, tabla 6.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>73 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: arm_id</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>diseno_adjudicado</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Diseño adjudicado</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: diseno_adjudicado</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>n_exito</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Éxito clínico (n)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: n_exito</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>N_brazo</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Pacientes en el brazo (N)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: N_brazo</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>¿Texto completo obtenido?</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: texto_completo</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: diseño comparativo</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: diseno_comparativo</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>denominador_valido</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: denominador válido</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: denominador_valido</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>numerador_valido</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: numerador válido</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: numerador_valido</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>definicion_operativa</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: definición operativa de éxito</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: definicion_operativa</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>atribuible_a_P_aeruginosa</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: atribuible a P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: atribuible_a_P_aeruginosa</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>terapeutica_no_profilactica</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: terapéutica, no profiláctica</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: terapeutica_no_profilactica</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>proporcion_no_tiempo</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Requisito: proporción, no tiempo</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: proporcion_no_tiempo</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>primer_requisito_que_falla</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Primer requisito que falla</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>columna interna: primer_requisito_que_falla</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>columna interna: motivo</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -765,83 +783,83 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>diseno_adjudicado</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>n_exito</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>N_brazo</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Diseño adjudicado</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Éxito clínico (n)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Pacientes en el brazo (N)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>¿Texto completo obtenido?</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>diseno_comparativo</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
-        <is>
-          <t>denominador_valido</t>
-        </is>
-      </c>
-      <c r="I1" s="8" t="inlineStr">
-        <is>
-          <t>numerador_valido</t>
-        </is>
-      </c>
-      <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>definicion_operativa</t>
-        </is>
-      </c>
-      <c r="K1" s="8" t="inlineStr">
-        <is>
-          <t>atribuible_a_P_aeruginosa</t>
-        </is>
-      </c>
-      <c r="L1" s="8" t="inlineStr">
-        <is>
-          <t>terapeutica_no_profilactica</t>
-        </is>
-      </c>
-      <c r="M1" s="8" t="inlineStr">
-        <is>
-          <t>proporcion_no_tiempo</t>
-        </is>
-      </c>
-      <c r="N1" s="8" t="inlineStr">
-        <is>
-          <t>primer_requisito_que_falla</t>
-        </is>
-      </c>
-      <c r="O1" s="8" t="inlineStr">
-        <is>
-          <t>motivo</t>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: diseño comparativo</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: denominador válido</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: numerador válido</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: definición operativa de éxito</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: atribuible a P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: terapéutica, no profiláctica</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Requisito: proporción, no tiempo</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Primer requisito que falla</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Motivo</t>
         </is>
       </c>
     </row>
@@ -913,7 +931,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -990,7 +1008,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1067,7 +1085,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1144,7 +1162,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1221,7 +1239,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1298,7 +1316,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1375,7 +1393,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1452,7 +1470,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1529,7 +1547,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>definición operativa de éxito</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1606,7 +1624,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1683,7 +1701,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1760,7 +1778,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1837,7 +1855,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1914,7 +1932,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1991,7 +2009,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2068,7 +2086,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2145,7 +2163,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2222,7 +2240,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2299,7 +2317,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2376,7 +2394,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2453,7 +2471,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>proporcion_no_tiempo</t>
+          <t>proporción, no tiempo</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2530,7 +2548,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2607,7 +2625,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2684,7 +2702,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2761,7 +2779,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2838,7 +2856,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2915,7 +2933,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2992,7 +3010,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3069,7 +3087,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3146,7 +3164,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3223,7 +3241,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3300,7 +3318,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3377,7 +3395,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3454,7 +3472,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3531,7 +3549,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3608,7 +3626,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3685,7 +3703,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3762,7 +3780,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3839,7 +3857,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3916,7 +3934,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3993,7 +4011,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4070,7 +4088,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4147,7 +4165,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4224,7 +4242,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>definicion_operativa</t>
+          <t>definición operativa de éxito</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4301,7 +4319,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4378,7 +4396,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4455,7 +4473,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4532,7 +4550,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4609,7 +4627,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4686,7 +4704,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4763,7 +4781,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4840,7 +4858,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4917,7 +4935,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4994,7 +5012,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5071,7 +5089,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5148,7 +5166,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5225,7 +5243,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5302,7 +5320,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5379,7 +5397,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5456,7 +5474,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5533,7 +5551,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5610,7 +5628,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5687,7 +5705,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5764,7 +5782,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5841,7 +5859,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5918,7 +5936,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5995,7 +6013,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6072,7 +6090,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>atribuible_a_P_aeruginosa</t>
+          <t>atribuible a P. aeruginosa</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6149,7 +6167,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>numerador_valido</t>
+          <t>numerador válido</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6226,7 +6244,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6303,7 +6321,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6380,7 +6398,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6457,7 +6475,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>diseno_comparativo</t>
+          <t>diseño comparativo</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">

--- a/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
+++ b/verificables revisión sistemática/S17_tabla6_brazo_a_brazo.xlsx
@@ -751,7 +751,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
